--- a/Catering_Present/jayraldines_catering/jayraldines_bookings_export.xlsx
+++ b/Catering_Present/jayraldines_catering/jayraldines_bookings_export.xlsx
@@ -455,24 +455,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="63" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="244" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -555,70 +555,70 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BKG-002</t>
+          <t>BK-1378</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Capt. Juanito Dela Cruz</t>
+          <t>ABOITIZ</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>09182223344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>juanito.dc@example.com</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sep 12, 2026</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Birthday</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Lahug Clubhouse</t>
+          <t>Catering Venue</t>
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>28,000.00</t>
+          <t>35,000.00</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>14,000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>14,000.00</t>
+          <t>35,000.00</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>GCash</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -626,73 +626,4615 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BKG-001</t>
+          <t>BK-1376</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Engr. Rodrigo Tan</t>
+          <t>Kaira Abellar</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>09178889900</t>
+          <t>+63 949 736 2679</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>rodrigo.tan@example.com</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sep 12, 2026</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Christening</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>sky blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BK-1375</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Glydel Abatol</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>+63 917 914 4287</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>jayraldine catering</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>16,000.00</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>16,000.00</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Blue royan and orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BK-1372</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>trixy  Sue Dionela</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>+63 927 908 8381</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Purple / Rapunziel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BK-1371</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Haibe A Candido</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>+63 922 489 9250</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>hush garden event place</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>27,000.00</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>safari</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BK-1142</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>jaric Alvarez</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>9473412827</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>50th birthday</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>36,400.00</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>36,400.00</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BK-1141</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Corazon Manalo</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>9950054843</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>General hardware</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>17,500.00</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>17,500.00</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BK-1140</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Jenny  mae Ignario</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>9294798419</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>1st Birthday</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Jayraldine Venue</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>50,600.00</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>50,600.00</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BK-1139</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Canread Maria</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Baptism</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Residence</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>18,000.00</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>18,000.00</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BK-1138</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Aimee ann Rizalde</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>9161385498</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Christianing</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Julians Apartment</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>22,500.00</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>22,500.00</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BK-1137</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Merrly Grace Cayne</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>9321262034</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>70th Birthday</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Beside capitol parish gym</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>23,490.00</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>23,490.00</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BK-1136</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Kyara Timoneth</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>94554177005</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1st Birthday</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Symfore Nichols Bassa tower</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>19,900.00</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>19,900.00</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BK-1135</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Anit Hisoler</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>9260878234</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>60th Birthday</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BK-1134</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Ryan Cañete</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>9086630345</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Baptism</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>34,000.00</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>34,000.00</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BK-1133</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Mark giovani R.Demonterde</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>9223708504</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Catering Venue</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BK-1132</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Athena Inago</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BK-1131</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kyla nacar</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>9454517140</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>3rd birthday</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>42,000.00</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>42,000.00</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BK-1130</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Anisa</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1st Birthday</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Residence</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>23,100.00</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>23,100.00</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BK-1129</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Mislang Angel</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>9617730143</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>BK-1128</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Quennie Quiñanola</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>9202085565</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>60th Birthday</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>26,900.00</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>26,900.00</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BK-1127</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>John narcisus villegis</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>9275903976</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Wedding</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Grand Ballroom Cebu</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>BK-1126</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Zaun Lei</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Catering Event</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LCM-basilica Minor Sto.niño</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BK-1125</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Hazel Tabuena</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4:30 PM</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Baptism</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Mobolo Church</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>BK-1124</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Jhanesse Magdasal</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>9816646017</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Renewal of Vows</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Catering Venue</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BK-1123</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Glymarie Pinar</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>60th Birthday</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>37,900.00</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>37,900.00</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>BK-1122</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Ethelle Kate Fernando</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>9271292179</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Baptism</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BK-1121</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Nenetle Alvarez</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>9088837084</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>House</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>63-E Urgello st. cebu city</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>30,250.00</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>30,250.00</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>BK-1120</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Larah marie Perdiguez</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>9287165430</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>21th Birthday</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Alliance of two hearts</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>31,500.00</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>31,500.00</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BK-1119</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Cindy mae Labor</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>9661803359</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Baptism</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>36,600.00</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>36,600.00</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>BK-1118</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Cristine Godinez</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>9772850182</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BK-1117</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Ma. Isabelle Juntong</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>9458662594</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>BK-1116</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>James R. Alvarado</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>9393798975</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Dinner Forecast</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>SMASN covered court</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>BK-1115</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Mary rose L Fernadez</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>9613401511</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Baptism</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>BK-1114</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Eunicah Delfino</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>+63 000 000 0000</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Client Venue</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>18,000.00</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>18,000.00</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Order entry with PARTY PACKAGE 32K</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>BK-1113</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Gayle Manigos Baella</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>9284672682</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>40days</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Client Venue</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>21,000.00</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>21,000.00</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>Light Blue  &amp; White</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>BK-1112</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Arlene Yap</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>+63 992 458 3720</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Food packs</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Cebu City</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>4,800.00</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>8,800.00</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>food pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>BK-1111</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Divine Denola</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>9566230422</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>50,150.00</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>50,150.00</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>Bear theme for twins, Cream Biege, Dusty Blue, Blush pink
+[Add-ons: photo both (+₱3,500.00), ice cream (+₱300.00), lechon (+₱500.00), food (+₱500.00), rice (+₱400.00), service charge (+₱1,000.00), table (+₱1,200.00), soft drinks (+₱750.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>BK-1110</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Brillant Jacob / Chef Pablo</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>+63 995 471 8389</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Fiesta</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Intrasco L Gabuya</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>21,000.00</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>21,000.00</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>Red &amp; White</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>BK-1109</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Charmine Ramos</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>+63 945 154 1664</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Christening</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Cebu City</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>42,800.00</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>42,800.00</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>Blue &amp; Pink
+[Add-ons: Corkage fee (+₱500.00), Corkage fee (+₱300.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>BK-1108</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Earol John Torres</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>9564489365</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>55,200.00</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>Princess
+[Add-ons: food both (+₱2,000.00), corkage (+₱1,000.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>BK-1107</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Lai Cabajar</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>+63 000 000 0000</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Food packs</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Client Venue</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>4,800.00</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>4,800.00</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>Food packs</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>BK-1106</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Errick Erasmo</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>9664114079</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Client Venue</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>33,200.00</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>33,200.00</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>Pastel Pink, Pastel Colors</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>BK-1105</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Mam Marian</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>+63 000 000 0000</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Food packs</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Cebu City</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>4,800.00</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>4,800.00</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>Add-ons: + (+₱1,000.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>BK-1104</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Rochelle Baldes Pinosa</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>+63 923 182 7860</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Food packs</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>UN1 -ORIENT TRAVEL INC CAPITOL SQUARE ESCARIO ST. CEBU CITY</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>4,050.00</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>4,050.00</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>BK-1103</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Kathleen Ybas</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>900520932287</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>65,760.00</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>65,760.00</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>Dusty blue, Tidy Power Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>BK-1102</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Karen jane Sinadjan</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>+63 092 242 4115</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Christening</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Small Venue</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>BK-1101</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Juvlyn Espinosa</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>+63 927 399 1793</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>big venue</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>28,000.00</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>28,000.00</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>light Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>BK-1100</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Iriza Sasam</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>+63 969 633 7235</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>37,400.00</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>37,400.00</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>Royal Blue
+[Add-ons: + (+₱2,400.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>BK-1099</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Corazon Manalo</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>9950054843</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Nicks hardware</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>37,000.00</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>15,000.00</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>22,000.00</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>Blue
+[Add-ons: + (+₱2,000.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>BK-1098</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Floriza Macalipay</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>+63 099 750 0655</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>28,000.00</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>7,000.00</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>Phantoms</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>BK-1097</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Ahmed Navaya</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>99662480392</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Big venue</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>42,000.00</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>37,000.00</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>Yellow Daisy Theme</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>BK-1373</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>ASHLEY B. DAAN</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>9420548850</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Catering Venue</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>CANCELLED</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>BK-1096</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Neschie Punay</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>+63 995 844 3319</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Christening</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>42,000.00</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>37,000.00</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>Blue &amp; Brown/ Hot Air Ballon/ 42k 100 pcks No Lechon</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>BK-1095</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Rovie jane T. Barcolo</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>+63 926 933 1858</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Big Venue</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>36,000.00</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>1,000.00</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>Pink and White</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>BK-1094</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Chrisviaj Marie L. Campaña</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>+63 993 905 3819</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Big venue</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>42,000.00</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>37,000.00</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>Fairy ( butterfly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>BK-1093</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Ma.Zyrine Alexa Genandy</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>+63 992 883 0924</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>small venue</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>to be followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>BK-1092</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Judielyn Coyaca</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>+63 999 372 7555</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Food packs</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>CHATEAU DE BUSAY</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>15,000.00</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>15,000.00</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>BK-1091</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>ROSE ANN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>+63 945 569 4057</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>SMALL VENUE</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>33,500.00</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>28,500.00</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>BOSS BABY
+[Add-ons: + (+₱1,500.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>BK-1090</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Maricis Pacaña</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>+63 927 533 7389</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>small venue</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>20,000.00</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>15,000.00</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>biege</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>BK-1089</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>kennith Villahermosa</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>9352518930</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>big venue</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>45,000.00</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>Pink
+special Instruction : Cake ALL White , Flowers Pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>BK-1088</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Clarice D, Luzano</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>+63 939 581 181</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>small venue</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>32,000.00</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>27,000.00</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>Little Prince Gold royal,blue , white</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>BK-1087</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Donnah Jane Navarro</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>+63 098 976 5046</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Kinasang-an cebu city</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>35,000.00</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>30,000.00</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>Biege or any light bown</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>BK-1086</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Jan Felix Karlmel Urlarte</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>+63 995 615 3326</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>5:01 PM</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Villa Esperanza</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>56,000.00</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>51,000.00</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>Rusty/Orange
+[Add-ons: Photo booth (+₱3,500.00)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>BK-1085</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Czakian junhilla</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>+63 976 421 2835</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Debut</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Big venue</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>45,000.00</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>45,000.00</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>5,000.00</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>40,000.00</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
